--- a/Sample_run/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Sample_run/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>40726</x:v>
+        <x:v>33640</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1681,7 +1681,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q13" s="0">
-        <x:v>40726</x:v>
+        <x:v>33640</x:v>
       </x:c>
       <x:c r="R13" s="4" t="s">
         <x:v>62</x:v>
